--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_15-07-2025.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error: ("Connection broken: InvalidChunkLength(got length b'', 0 bytes read)", InvalidChunkLength(got length b'', 0 bytes read))</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>£31.22</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>Error: 502 Server Error: Bad Gateway for url: https://insulation4less.co.uk/products/140mm-celotex-xr4140-2-4m-x-1-2m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
